--- a/config/yunying/jifu_task.xlsx
+++ b/config/yunying/jifu_task.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="jifu_task" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jifu_task" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1271,10 +1271,9 @@
           <t>600</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>ノーマルステージに600回挑戦</t>
+          <t>挑战普通关卡600次</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1334,10 +1333,9 @@
           <t>50</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>パートナーが50回突破</t>
+          <t>合作伙伴突破50次</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1404,7 +1402,7 @@
       </c>
       <c r="G6" s="1" t="inlineStr">
         <is>
-          <t>時空激戦で7層を累計3回クリア</t>
+          <t>时空激战累计3次通关7层</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1464,10 +1462,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" s="1" t="inlineStr">
         <is>
-          <t>累計ログイン5日</t>
+          <t>累计登录5天</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1495,7 +1492,6 @@
           <t>{gold=100000;520=1}</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1523,10 +1519,9 @@
           <t>20000000</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>計20000000金貨を消費</t>
+          <t>共消耗20000000金币</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1554,7 +1549,6 @@
           <t>{gold=100000;901=10}</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1582,10 +1576,9 @@
           <t>30</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>ダイヤガチャを30回到達</t>
+          <t>达到30次钻石扭蛋</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1645,10 +1638,9 @@
           <t>150</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" s="1" t="inlineStr">
         <is>
-          <t>精鋭ステージに150回挑戦</t>
+          <t>挑战150次精英关卡</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1715,7 +1707,7 @@
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
-          <t>Lv.S以上の依頼を25回クリア</t>
+          <t>完成25次Lv.S以上的请求</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1775,10 +1767,9 @@
           <t>200</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" s="1" t="inlineStr">
         <is>
-          <t>仲間を累計200回レベルアップ</t>
+          <t>累计升级200次伙伴</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1838,10 +1829,9 @@
           <t>3000</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" s="1" t="inlineStr">
         <is>
-          <t>計3000ダイヤ消費</t>
+          <t>共消费钻石3000颗</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1869,7 +1859,6 @@
           <t>{gold=100000;529=500}</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1897,10 +1886,9 @@
           <t>20</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>スタミナを20回購入</t>
+          <t>购买20次耐力</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1960,10 +1948,9 @@
           <t>60</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" s="1" t="inlineStr">
         <is>
-          <t>累計60回回収行う</t>
+          <t>累计回收60次</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2023,10 +2010,9 @@
           <t>50</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" s="1" t="inlineStr">
         <is>
-          <t>アリーナで計50回戦闘</t>
+          <t>在竞技场共战斗50次</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2086,10 +2072,9 @@
           <t>200</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>スキルを200回レベルアップ</t>
+          <t>技能提升200次</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2149,10 +2134,9 @@
           <t>40</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>ギルド寄付40回</t>
+          <t>公会捐赠40次</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2212,10 +2196,9 @@
           <t>20</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" s="1" t="inlineStr">
         <is>
-          <t>パートナーの星ランクが20回UP</t>
+          <t>合作伙伴星级提升20倍</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
